--- a/artfynd/A 2694-2024 artfynd.xlsx
+++ b/artfynd/A 2694-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121143140</v>
+        <v>121143142</v>
       </c>
       <c r="B2" t="n">
-        <v>100337</v>
+        <v>100347</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495046</v>
+        <v>495028</v>
       </c>
       <c r="R2" t="n">
-        <v>6542160</v>
+        <v>6542146</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -788,7 +788,7 @@
         <v>121143141</v>
       </c>
       <c r="B3" t="n">
-        <v>100337</v>
+        <v>100347</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121143143</v>
+        <v>121143140</v>
       </c>
       <c r="B4" t="n">
-        <v>100337</v>
+        <v>100347</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495031</v>
+        <v>495046</v>
       </c>
       <c r="R4" t="n">
-        <v>6542136</v>
+        <v>6542160</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121143142</v>
+        <v>121143143</v>
       </c>
       <c r="B5" t="n">
-        <v>100337</v>
+        <v>100347</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495028</v>
+        <v>495031</v>
       </c>
       <c r="R5" t="n">
-        <v>6542146</v>
+        <v>6542136</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 2694-2024 artfynd.xlsx
+++ b/artfynd/A 2694-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121143142</v>
+        <v>121143140</v>
       </c>
       <c r="B2" t="n">
         <v>100347</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495028</v>
+        <v>495046</v>
       </c>
       <c r="R2" t="n">
-        <v>6542146</v>
+        <v>6542160</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121143141</v>
+        <v>121143143</v>
       </c>
       <c r="B3" t="n">
         <v>100347</v>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495039</v>
+        <v>495031</v>
       </c>
       <c r="R3" t="n">
-        <v>6542148</v>
+        <v>6542136</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,7 +895,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121143140</v>
+        <v>121143141</v>
       </c>
       <c r="B4" t="n">
         <v>100347</v>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495046</v>
+        <v>495039</v>
       </c>
       <c r="R4" t="n">
-        <v>6542160</v>
+        <v>6542148</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,7 +1005,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121143143</v>
+        <v>121143142</v>
       </c>
       <c r="B5" t="n">
         <v>100347</v>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495031</v>
+        <v>495028</v>
       </c>
       <c r="R5" t="n">
-        <v>6542136</v>
+        <v>6542146</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 2694-2024 artfynd.xlsx
+++ b/artfynd/A 2694-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121143140</v>
+        <v>121143141</v>
       </c>
       <c r="B2" t="n">
-        <v>100347</v>
+        <v>100360</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495046</v>
+        <v>495039</v>
       </c>
       <c r="R2" t="n">
-        <v>6542160</v>
+        <v>6542148</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -788,7 +788,7 @@
         <v>121143143</v>
       </c>
       <c r="B3" t="n">
-        <v>100347</v>
+        <v>100360</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121143141</v>
+        <v>121143142</v>
       </c>
       <c r="B4" t="n">
-        <v>100347</v>
+        <v>100360</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495039</v>
+        <v>495028</v>
       </c>
       <c r="R4" t="n">
-        <v>6542148</v>
+        <v>6542146</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121143142</v>
+        <v>121143140</v>
       </c>
       <c r="B5" t="n">
-        <v>100347</v>
+        <v>100360</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495028</v>
+        <v>495046</v>
       </c>
       <c r="R5" t="n">
-        <v>6542146</v>
+        <v>6542160</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 2694-2024 artfynd.xlsx
+++ b/artfynd/A 2694-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121143141</v>
       </c>
       <c r="B2" t="n">
-        <v>100360</v>
+        <v>100361</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>121143143</v>
       </c>
       <c r="B3" t="n">
-        <v>100360</v>
+        <v>100361</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>121143142</v>
       </c>
       <c r="B4" t="n">
-        <v>100360</v>
+        <v>100361</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>121143140</v>
       </c>
       <c r="B5" t="n">
-        <v>100360</v>
+        <v>100361</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 2694-2024 artfynd.xlsx
+++ b/artfynd/A 2694-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121143141</v>
       </c>
       <c r="B2" t="n">
-        <v>100361</v>
+        <v>100364</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>121143143</v>
       </c>
       <c r="B3" t="n">
-        <v>100361</v>
+        <v>100364</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121143142</v>
+        <v>121143140</v>
       </c>
       <c r="B4" t="n">
-        <v>100361</v>
+        <v>100364</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495028</v>
+        <v>495046</v>
       </c>
       <c r="R4" t="n">
-        <v>6542146</v>
+        <v>6542160</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121143140</v>
+        <v>121143142</v>
       </c>
       <c r="B5" t="n">
-        <v>100361</v>
+        <v>100364</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495046</v>
+        <v>495028</v>
       </c>
       <c r="R5" t="n">
-        <v>6542160</v>
+        <v>6542146</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 2694-2024 artfynd.xlsx
+++ b/artfynd/A 2694-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121143141</v>
+        <v>121143143</v>
       </c>
       <c r="B2" t="n">
         <v>100364</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495039</v>
+        <v>495031</v>
       </c>
       <c r="R2" t="n">
-        <v>6542148</v>
+        <v>6542136</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121143143</v>
+        <v>121143140</v>
       </c>
       <c r="B3" t="n">
         <v>100364</v>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495031</v>
+        <v>495046</v>
       </c>
       <c r="R3" t="n">
-        <v>6542136</v>
+        <v>6542160</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,7 +895,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121143140</v>
+        <v>121143141</v>
       </c>
       <c r="B4" t="n">
         <v>100364</v>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495046</v>
+        <v>495039</v>
       </c>
       <c r="R4" t="n">
-        <v>6542160</v>
+        <v>6542148</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 2694-2024 artfynd.xlsx
+++ b/artfynd/A 2694-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121143143</v>
+        <v>121143140</v>
       </c>
       <c r="B2" t="n">
-        <v>100364</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495031</v>
+        <v>495046</v>
       </c>
       <c r="R2" t="n">
-        <v>6542136</v>
+        <v>6542160</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,15 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121143140</v>
+        <v>121143141</v>
       </c>
       <c r="B3" t="n">
-        <v>100364</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -833,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495046</v>
+        <v>495039</v>
       </c>
       <c r="R3" t="n">
-        <v>6542160</v>
+        <v>6542148</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,15 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121143141</v>
+        <v>121143142</v>
       </c>
       <c r="B4" t="n">
-        <v>100364</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -943,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495039</v>
+        <v>495028</v>
       </c>
       <c r="R4" t="n">
-        <v>6542148</v>
+        <v>6542146</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,15 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121143142</v>
+        <v>121143143</v>
       </c>
       <c r="B5" t="n">
-        <v>100364</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1053,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495028</v>
+        <v>495031</v>
       </c>
       <c r="R5" t="n">
-        <v>6542146</v>
+        <v>6542136</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 2694-2024 artfynd.xlsx
+++ b/artfynd/A 2694-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121143140</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121143141</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121143142</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,8 +1112,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121143143</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>